--- a/report-008-manual-008.xlsx
+++ b/report-008-manual-008.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>{"baseline_commit": "7c6c25a95c401ec28b9adc43e14cecfb406cc120", "fix_commit": "65fed87a7f590cd7d9b43dbac3639d1aab247171", "fix_passed": true, "red_failed": true, "test_commit": "7521ef938cf40423f5e3105d960a2fa1d0d16911"}</t>
+          <t>{"pre_fix": {"commit": "7521ef938cf40423f5e3105d960a2fa1d0d16911", "result": "red", "trajectory_url": "未生成"}}</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
